--- a/tasks/xlsx/cowork-bench-sf-sla-breach-audit/solution/SLA_Breach_Audit.xlsx
+++ b/tasks/xlsx/cowork-bench-sf-sla-breach-audit/solution/SLA_Breach_Audit.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Breach Analysis" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escalation Draft" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Breach Analysis'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Escalation Draft'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -769,4 +771,127 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>sla-audit@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>ops-director@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>SLA Breach Audit Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>The SLA breach audit is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Overall_Breach_Rate</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>79.02</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Worst_Priority</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>SLA_Breach_Audit.xlsx</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B8"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;CCowork-Bench 静态快照 · SLA Breach Audit</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
 </file>